--- a/data/nzd0383/nzd0383.xlsx
+++ b/data/nzd0383/nzd0383.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K596"/>
+  <dimension ref="A1:K597"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23688,6 +23688,45 @@
         <v>283.59</v>
       </c>
       <c r="K596" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:19:53+00:00</t>
+        </is>
+      </c>
+      <c r="B597" t="n">
+        <v>314.69</v>
+      </c>
+      <c r="C597" t="n">
+        <v>323.59</v>
+      </c>
+      <c r="D597" t="n">
+        <v>334.44</v>
+      </c>
+      <c r="E597" t="n">
+        <v>338.25</v>
+      </c>
+      <c r="F597" t="n">
+        <v>340.39</v>
+      </c>
+      <c r="G597" t="n">
+        <v>341.27</v>
+      </c>
+      <c r="H597" t="n">
+        <v>332.93</v>
+      </c>
+      <c r="I597" t="n">
+        <v>322.81</v>
+      </c>
+      <c r="J597" t="n">
+        <v>285.94</v>
+      </c>
+      <c r="K597" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -23704,7 +23743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B606"/>
+  <dimension ref="A1:B607"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29767,6 +29806,16 @@
       </c>
       <c r="B606" t="n">
         <v>-0.41</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B607" t="n">
+        <v>0.95</v>
       </c>
     </row>
   </sheetData>
@@ -29935,28 +29984,28 @@
         <v>0.055</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3443191194143346</v>
+        <v>-0.3516726387438993</v>
       </c>
       <c r="J2" t="n">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="K2" t="n">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03226098086247686</v>
+        <v>0.0336100046348089</v>
       </c>
       <c r="M2" t="n">
-        <v>11.39590595381591</v>
+        <v>11.41264650441992</v>
       </c>
       <c r="N2" t="n">
-        <v>194.8022403872644</v>
+        <v>195.2258491587171</v>
       </c>
       <c r="O2" t="n">
-        <v>13.95715731756522</v>
+        <v>13.97232440071147</v>
       </c>
       <c r="P2" t="n">
-        <v>344.9390784468997</v>
+        <v>345.0131814044821</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -30013,28 +30062,28 @@
         <v>0.0579</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4026154781742721</v>
+        <v>-0.4038077714509453</v>
       </c>
       <c r="J3" t="n">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="K3" t="n">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2051090927381368</v>
+        <v>0.2066275347005202</v>
       </c>
       <c r="M3" t="n">
-        <v>4.89176190047956</v>
+        <v>4.889044042679222</v>
       </c>
       <c r="N3" t="n">
-        <v>34.41078136024553</v>
+        <v>34.37277401950194</v>
       </c>
       <c r="O3" t="n">
-        <v>5.866070350775341</v>
+        <v>5.862829864451291</v>
       </c>
       <c r="P3" t="n">
-        <v>337.6058333667661</v>
+        <v>337.6178483563442</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30091,28 +30140,28 @@
         <v>0.0607</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1592587693532895</v>
+        <v>-0.1605179445636275</v>
       </c>
       <c r="J4" t="n">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="K4" t="n">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04946629114399148</v>
+        <v>0.05036129658275568</v>
       </c>
       <c r="M4" t="n">
-        <v>4.016331773288291</v>
+        <v>4.015174046493699</v>
       </c>
       <c r="N4" t="n">
-        <v>26.69659477058879</v>
+        <v>26.67380616611189</v>
       </c>
       <c r="O4" t="n">
-        <v>5.166874758554613</v>
+        <v>5.164669027741457</v>
       </c>
       <c r="P4" t="n">
-        <v>342.252440539138</v>
+        <v>342.2651295119983</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30169,28 +30218,28 @@
         <v>0.0618</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2193594914958309</v>
+        <v>-0.2212269615035838</v>
       </c>
       <c r="J5" t="n">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="K5" t="n">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08445245621999309</v>
+        <v>0.0859494726288712</v>
       </c>
       <c r="M5" t="n">
-        <v>4.378421366185536</v>
+        <v>4.380584028355337</v>
       </c>
       <c r="N5" t="n">
-        <v>28.57409359479018</v>
+        <v>28.57455025312319</v>
       </c>
       <c r="O5" t="n">
-        <v>5.345474122544247</v>
+        <v>5.345516836857143</v>
       </c>
       <c r="P5" t="n">
-        <v>349.3936293157001</v>
+        <v>349.412448202898</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30247,28 +30296,28 @@
         <v>0.053</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3234921811219915</v>
+        <v>-0.3249514207348053</v>
       </c>
       <c r="J6" t="n">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="K6" t="n">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1723157087443268</v>
+        <v>0.1740159537731196</v>
       </c>
       <c r="M6" t="n">
-        <v>4.161726081209172</v>
+        <v>4.162467908434667</v>
       </c>
       <c r="N6" t="n">
-        <v>27.5333086451887</v>
+        <v>27.51666397886933</v>
       </c>
       <c r="O6" t="n">
-        <v>5.247219134473869</v>
+        <v>5.245632848271915</v>
       </c>
       <c r="P6" t="n">
-        <v>353.0916906946724</v>
+        <v>353.1063957585044</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30325,28 +30374,28 @@
         <v>0.0557</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2492184292770092</v>
+        <v>-0.2513457675795324</v>
       </c>
       <c r="J7" t="n">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="K7" t="n">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1359942949481641</v>
+        <v>0.1381280936997938</v>
       </c>
       <c r="M7" t="n">
-        <v>3.829880964167846</v>
+        <v>3.833232842562489</v>
       </c>
       <c r="N7" t="n">
-        <v>21.61460056247268</v>
+        <v>21.64114161058144</v>
       </c>
       <c r="O7" t="n">
-        <v>4.64915052052229</v>
+        <v>4.652004042408114</v>
       </c>
       <c r="P7" t="n">
-        <v>353.9526443139844</v>
+        <v>353.9740819485278</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30403,28 +30452,28 @@
         <v>0.0546</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.134869235273387</v>
+        <v>-0.1375268836521225</v>
       </c>
       <c r="J8" t="n">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="K8" t="n">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03615630345387566</v>
+        <v>0.03755059550480999</v>
       </c>
       <c r="M8" t="n">
-        <v>4.197829887159461</v>
+        <v>4.203075875147452</v>
       </c>
       <c r="N8" t="n">
-        <v>26.56069064546919</v>
+        <v>26.61414941984109</v>
       </c>
       <c r="O8" t="n">
-        <v>5.153706495859964</v>
+        <v>5.158890328340107</v>
       </c>
       <c r="P8" t="n">
-        <v>344.141451748402</v>
+        <v>344.1682334288807</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30481,28 +30530,28 @@
         <v>0.0518</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2115621836582733</v>
+        <v>-0.2132743705109652</v>
       </c>
       <c r="J9" t="n">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="K9" t="n">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06325515184044672</v>
+        <v>0.06438718158251522</v>
       </c>
       <c r="M9" t="n">
-        <v>4.960917862126459</v>
+        <v>4.959429700193582</v>
       </c>
       <c r="N9" t="n">
-        <v>36.30717658703872</v>
+        <v>36.2869438809623</v>
       </c>
       <c r="O9" t="n">
-        <v>6.025543675639462</v>
+        <v>6.023864530429142</v>
       </c>
       <c r="P9" t="n">
-        <v>333.3010055798673</v>
+        <v>333.318259646122</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30559,28 +30608,28 @@
         <v>0.08550000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3239280965099586</v>
+        <v>-0.3354831017013117</v>
       </c>
       <c r="J10" t="n">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="K10" t="n">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01259102844170013</v>
+        <v>0.01349084649233823</v>
       </c>
       <c r="M10" t="n">
-        <v>17.27283489628413</v>
+        <v>17.31116383701039</v>
       </c>
       <c r="N10" t="n">
-        <v>450.7379101353867</v>
+        <v>451.8346422403903</v>
       </c>
       <c r="O10" t="n">
-        <v>21.23058901998215</v>
+        <v>21.25640238235037</v>
       </c>
       <c r="P10" t="n">
-        <v>327.7739409442452</v>
+        <v>327.8903831566313</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -30622,7 +30671,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K596"/>
+  <dimension ref="A1:K597"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64597,6 +64646,63 @@
         </is>
       </c>
     </row>
+    <row r="597">
+      <c r="A597" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:19:53+00:00</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>-42.123047485152476,171.3282919035113</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>-42.122379951139074,171.32843419183934</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>-42.121701458117535,171.32851456878618</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>-42.121038211564844,171.3286544166664</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>-42.12037369820114,171.3287634831031</t>
+        </is>
+      </c>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>-42.11970949810999,171.32888745752317</t>
+        </is>
+      </c>
+      <c r="H597" t="inlineStr">
+        <is>
+          <t>-42.1190410209556,171.32900884025156</t>
+        </is>
+      </c>
+      <c r="I597" t="inlineStr">
+        <is>
+          <t>-42.118363680943645,171.32913256742071</t>
+        </is>
+      </c>
+      <c r="J597" t="inlineStr">
+        <is>
+          <t>-42.117662661457224,171.32949063526038</t>
+        </is>
+      </c>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0383/nzd0383.xlsx
+++ b/data/nzd0383/nzd0383.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K597"/>
+  <dimension ref="A1:K598"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23727,6 +23727,45 @@
         <v>285.94</v>
       </c>
       <c r="K597" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-16 22:13:32+00:00</t>
+        </is>
+      </c>
+      <c r="B598" t="n">
+        <v>316.83</v>
+      </c>
+      <c r="C598" t="n">
+        <v>323.74</v>
+      </c>
+      <c r="D598" t="n">
+        <v>334.23</v>
+      </c>
+      <c r="E598" t="n">
+        <v>338.85</v>
+      </c>
+      <c r="F598" t="n">
+        <v>341.93</v>
+      </c>
+      <c r="G598" t="n">
+        <v>342.17</v>
+      </c>
+      <c r="H598" t="n">
+        <v>332.96</v>
+      </c>
+      <c r="I598" t="n">
+        <v>322.25</v>
+      </c>
+      <c r="J598" t="n">
+        <v>291.53</v>
+      </c>
+      <c r="K598" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -23743,7 +23782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B607"/>
+  <dimension ref="A1:B608"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29816,6 +29855,16 @@
       </c>
       <c r="B607" t="n">
         <v>0.95</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>2026-01-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B608" t="n">
+        <v>0.88</v>
       </c>
     </row>
   </sheetData>
@@ -29984,28 +30033,28 @@
         <v>0.055</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3516726387438993</v>
+        <v>-0.3582766262419173</v>
       </c>
       <c r="J2" t="n">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="K2" t="n">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0336100046348089</v>
+        <v>0.03487278500312152</v>
       </c>
       <c r="M2" t="n">
-        <v>11.41264650441992</v>
+        <v>11.42529507740476</v>
       </c>
       <c r="N2" t="n">
-        <v>195.2258491587171</v>
+        <v>195.4935065675501</v>
       </c>
       <c r="O2" t="n">
-        <v>13.97232440071147</v>
+        <v>13.98189924751105</v>
       </c>
       <c r="P2" t="n">
-        <v>345.0131814044821</v>
+        <v>345.0801647982005</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -30062,28 +30111,28 @@
         <v>0.0579</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4038077714509453</v>
+        <v>-0.4049294728834927</v>
       </c>
       <c r="J3" t="n">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="K3" t="n">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2066275347005202</v>
+        <v>0.2081193182441274</v>
       </c>
       <c r="M3" t="n">
-        <v>4.889044042679222</v>
+        <v>4.885985140376927</v>
       </c>
       <c r="N3" t="n">
-        <v>34.37277401950194</v>
+        <v>34.33235423258483</v>
       </c>
       <c r="O3" t="n">
-        <v>5.862829864451291</v>
+        <v>5.859381727843376</v>
       </c>
       <c r="P3" t="n">
-        <v>337.6178483563442</v>
+        <v>337.6292256293499</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30140,28 +30189,28 @@
         <v>0.0607</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1605179445636275</v>
+        <v>-0.1618433525127903</v>
       </c>
       <c r="J4" t="n">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="K4" t="n">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05036129658275568</v>
+        <v>0.05130575218048483</v>
       </c>
       <c r="M4" t="n">
-        <v>4.015174046493699</v>
+        <v>4.014248170997887</v>
       </c>
       <c r="N4" t="n">
-        <v>26.67380616611189</v>
+        <v>26.65307953163673</v>
       </c>
       <c r="O4" t="n">
-        <v>5.164669027741457</v>
+        <v>5.162662058631838</v>
       </c>
       <c r="P4" t="n">
-        <v>342.2651295119983</v>
+        <v>342.2785729539374</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30218,28 +30267,28 @@
         <v>0.0618</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2212269615035838</v>
+        <v>-0.2228746046707883</v>
       </c>
       <c r="J5" t="n">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="K5" t="n">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0859494726288712</v>
+        <v>0.0873399912369256</v>
       </c>
       <c r="M5" t="n">
-        <v>4.380584028355337</v>
+        <v>4.381509988052014</v>
       </c>
       <c r="N5" t="n">
-        <v>28.57455025312319</v>
+        <v>28.5637026477677</v>
       </c>
       <c r="O5" t="n">
-        <v>5.345516836857143</v>
+        <v>5.34450209540306</v>
       </c>
       <c r="P5" t="n">
-        <v>349.412448202898</v>
+        <v>349.4291600351069</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30296,28 +30345,28 @@
         <v>0.053</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3249514207348053</v>
+        <v>-0.3258586544068551</v>
       </c>
       <c r="J6" t="n">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="K6" t="n">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1740159537731196</v>
+        <v>0.1753415991039864</v>
       </c>
       <c r="M6" t="n">
-        <v>4.162467908434667</v>
+        <v>4.160252837055848</v>
       </c>
       <c r="N6" t="n">
-        <v>27.51666397886933</v>
+        <v>27.48179520991703</v>
       </c>
       <c r="O6" t="n">
-        <v>5.245632848271915</v>
+        <v>5.242308194861976</v>
       </c>
       <c r="P6" t="n">
-        <v>353.1063957585044</v>
+        <v>353.1155977126674</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30374,28 +30423,28 @@
         <v>0.0557</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2513457675795324</v>
+        <v>-0.2531495443732001</v>
       </c>
       <c r="J7" t="n">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="K7" t="n">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1381280936997938</v>
+        <v>0.1400774218738692</v>
       </c>
       <c r="M7" t="n">
-        <v>3.833232842562489</v>
+        <v>3.834976910751458</v>
       </c>
       <c r="N7" t="n">
-        <v>21.64114161058144</v>
+        <v>21.6492555492045</v>
       </c>
       <c r="O7" t="n">
-        <v>4.652004042408114</v>
+        <v>4.652876051347651</v>
       </c>
       <c r="P7" t="n">
-        <v>353.9740819485278</v>
+        <v>353.9923774239791</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30452,28 +30501,28 @@
         <v>0.0546</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1375268836521225</v>
+        <v>-0.1401751659511335</v>
       </c>
       <c r="J8" t="n">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="K8" t="n">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03755059550480999</v>
+        <v>0.0389701141064317</v>
       </c>
       <c r="M8" t="n">
-        <v>4.203075875147452</v>
+        <v>4.208225390204218</v>
       </c>
       <c r="N8" t="n">
-        <v>26.61414941984109</v>
+        <v>26.66519897258864</v>
       </c>
       <c r="O8" t="n">
-        <v>5.158890328340107</v>
+        <v>5.163835684119765</v>
       </c>
       <c r="P8" t="n">
-        <v>344.1682334288807</v>
+        <v>344.1950946147877</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30530,28 +30579,28 @@
         <v>0.0518</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2132743705109652</v>
+        <v>-0.2151740998413803</v>
       </c>
       <c r="J9" t="n">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="K9" t="n">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06438718158251522</v>
+        <v>0.06562746752203208</v>
       </c>
       <c r="M9" t="n">
-        <v>4.959429700193582</v>
+        <v>4.958677066382459</v>
       </c>
       <c r="N9" t="n">
-        <v>36.2869438809623</v>
+        <v>36.27537091671674</v>
       </c>
       <c r="O9" t="n">
-        <v>6.023864530429142</v>
+        <v>6.022903860823011</v>
       </c>
       <c r="P9" t="n">
-        <v>333.318259646122</v>
+        <v>333.3375283557821</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30608,28 +30657,28 @@
         <v>0.08550000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3354831017013117</v>
+        <v>-0.3450947798722035</v>
       </c>
       <c r="J10" t="n">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="K10" t="n">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01349084649233823</v>
+        <v>0.01428119986862053</v>
       </c>
       <c r="M10" t="n">
-        <v>17.31116383701039</v>
+        <v>17.3373568960232</v>
       </c>
       <c r="N10" t="n">
-        <v>451.8346422403903</v>
+        <v>452.337483007109</v>
       </c>
       <c r="O10" t="n">
-        <v>21.25640238235037</v>
+        <v>21.26822707719449</v>
       </c>
       <c r="P10" t="n">
-        <v>327.8903831566313</v>
+        <v>327.9878731690533</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -30671,7 +30720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K597"/>
+  <dimension ref="A1:K598"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64703,6 +64752,63 @@
         </is>
       </c>
     </row>
+    <row r="598">
+      <c r="A598" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-16 22:13:32+00:00</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>-42.12304200996249,171.32826708660528</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>-42.12237959612902,171.32843244136782</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>-42.12170189195787,171.32851704097328</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>-42.12103718622191,171.32864729165593</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>-42.12037145073341,171.3287451035169</t>
+        </is>
+      </c>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>-42.119708693452935,171.3288766261883</t>
+        </is>
+      </c>
+      <c r="H598" t="inlineStr">
+        <is>
+          <t>-42.119041014033655,171.32900847753697</t>
+        </is>
+      </c>
+      <c r="I598" t="inlineStr">
+        <is>
+          <t>-42.118363513207235,171.32913933649667</t>
+        </is>
+      </c>
+      <c r="J598" t="inlineStr">
+        <is>
+          <t>-42.117666772109764,171.32942325452547</t>
+        </is>
+      </c>
+      <c r="K598" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0383/nzd0383.xlsx
+++ b/data/nzd0383/nzd0383.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K598"/>
+  <dimension ref="A1:K599"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23766,6 +23766,45 @@
         <v>291.53</v>
       </c>
       <c r="K598" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:19:37+00:00</t>
+        </is>
+      </c>
+      <c r="B599" t="n">
+        <v>314.63</v>
+      </c>
+      <c r="C599" t="n">
+        <v>326.19</v>
+      </c>
+      <c r="D599" t="n">
+        <v>337.17</v>
+      </c>
+      <c r="E599" t="n">
+        <v>342.08</v>
+      </c>
+      <c r="F599" t="n">
+        <v>344.94</v>
+      </c>
+      <c r="G599" t="n">
+        <v>344.57</v>
+      </c>
+      <c r="H599" t="n">
+        <v>336.69</v>
+      </c>
+      <c r="I599" t="n">
+        <v>324.77</v>
+      </c>
+      <c r="J599" t="n">
+        <v>312.63</v>
+      </c>
+      <c r="K599" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -23782,7 +23821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B608"/>
+  <dimension ref="A1:B609"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29865,6 +29904,16 @@
       </c>
       <c r="B608" t="n">
         <v>0.88</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B609" t="n">
+        <v>-0.75</v>
       </c>
     </row>
   </sheetData>
@@ -30033,28 +30082,28 @@
         <v>0.055</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3582766262419173</v>
+        <v>-0.3655997572431984</v>
       </c>
       <c r="J2" t="n">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="K2" t="n">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03487278500312152</v>
+        <v>0.03627144705031426</v>
       </c>
       <c r="M2" t="n">
-        <v>11.42529507740476</v>
+        <v>11.44131453536513</v>
       </c>
       <c r="N2" t="n">
-        <v>195.4935065675501</v>
+        <v>195.896956843973</v>
       </c>
       <c r="O2" t="n">
-        <v>13.98189924751105</v>
+        <v>13.99631940347079</v>
       </c>
       <c r="P2" t="n">
-        <v>345.0801647982005</v>
+        <v>345.1546338093961</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -30111,28 +30160,28 @@
         <v>0.0579</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4049294728834927</v>
+        <v>-0.4051798232118687</v>
       </c>
       <c r="J3" t="n">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="K3" t="n">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2081193182441274</v>
+        <v>0.2089864180355184</v>
       </c>
       <c r="M3" t="n">
-        <v>4.885985140376927</v>
+        <v>4.878957861225541</v>
       </c>
       <c r="N3" t="n">
-        <v>34.33235423258483</v>
+        <v>34.27579584300464</v>
       </c>
       <c r="O3" t="n">
-        <v>5.859381727843376</v>
+        <v>5.854553428145023</v>
       </c>
       <c r="P3" t="n">
-        <v>337.6292256293499</v>
+        <v>337.6317714449857</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30189,28 +30238,28 @@
         <v>0.0607</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1618433525127903</v>
+        <v>-0.1621308757710853</v>
       </c>
       <c r="J4" t="n">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="K4" t="n">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05130575218048483</v>
+        <v>0.0516744698317021</v>
       </c>
       <c r="M4" t="n">
-        <v>4.014248170997887</v>
+        <v>4.008784506424503</v>
       </c>
       <c r="N4" t="n">
-        <v>26.65307953163673</v>
+        <v>26.60963504119652</v>
       </c>
       <c r="O4" t="n">
-        <v>5.162662058631838</v>
+        <v>5.158452775900591</v>
       </c>
       <c r="P4" t="n">
-        <v>342.2785729539374</v>
+        <v>342.2814967815649</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30267,28 +30316,28 @@
         <v>0.0618</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2228746046707883</v>
+        <v>-0.2233787288323817</v>
       </c>
       <c r="J5" t="n">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="K5" t="n">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0873399912369256</v>
+        <v>0.08801505917451302</v>
       </c>
       <c r="M5" t="n">
-        <v>4.381509988052014</v>
+        <v>4.376693594935007</v>
       </c>
       <c r="N5" t="n">
-        <v>28.5637026477677</v>
+        <v>28.51939840443152</v>
       </c>
       <c r="O5" t="n">
-        <v>5.34450209540306</v>
+        <v>5.340355644002702</v>
       </c>
       <c r="P5" t="n">
-        <v>349.4291600351069</v>
+        <v>349.4342864800424</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30345,28 +30394,28 @@
         <v>0.053</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3258586544068551</v>
+        <v>-0.3257005843022029</v>
       </c>
       <c r="J6" t="n">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="K6" t="n">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1753415991039864</v>
+        <v>0.1757843966420661</v>
       </c>
       <c r="M6" t="n">
-        <v>4.160252837055848</v>
+        <v>4.153973574925915</v>
       </c>
       <c r="N6" t="n">
-        <v>27.48179520991703</v>
+        <v>27.43617931683756</v>
       </c>
       <c r="O6" t="n">
-        <v>5.242308194861976</v>
+        <v>5.237955642885644</v>
       </c>
       <c r="P6" t="n">
-        <v>353.1155977126674</v>
+        <v>353.1139902957864</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30423,28 +30472,28 @@
         <v>0.0557</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2531495443732001</v>
+        <v>-0.254099222154365</v>
       </c>
       <c r="J7" t="n">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="K7" t="n">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1400774218738692</v>
+        <v>0.1414031696202405</v>
       </c>
       <c r="M7" t="n">
-        <v>3.834976910751458</v>
+        <v>3.832832070923424</v>
       </c>
       <c r="N7" t="n">
-        <v>21.6492555492045</v>
+        <v>21.62533558161371</v>
       </c>
       <c r="O7" t="n">
-        <v>4.652876051347651</v>
+        <v>4.65030489125323</v>
       </c>
       <c r="P7" t="n">
-        <v>353.9923774239791</v>
+        <v>354.0020347092721</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30501,28 +30550,28 @@
         <v>0.0546</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1401751659511335</v>
+        <v>-0.1415014979326486</v>
       </c>
       <c r="J8" t="n">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="K8" t="n">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0389701141064317</v>
+        <v>0.03980159249513193</v>
       </c>
       <c r="M8" t="n">
-        <v>4.208225390204218</v>
+        <v>4.207265922752671</v>
       </c>
       <c r="N8" t="n">
-        <v>26.66519897258864</v>
+        <v>26.64456627155733</v>
       </c>
       <c r="O8" t="n">
-        <v>5.163835684119765</v>
+        <v>5.161837489843838</v>
       </c>
       <c r="P8" t="n">
-        <v>344.1950946147877</v>
+        <v>344.2085821013783</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30579,28 +30628,28 @@
         <v>0.0518</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2151740998413803</v>
+        <v>-0.216176772177166</v>
       </c>
       <c r="J9" t="n">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="K9" t="n">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06562746752203208</v>
+        <v>0.06642679635489035</v>
       </c>
       <c r="M9" t="n">
-        <v>4.958677066382459</v>
+        <v>4.954376652175919</v>
       </c>
       <c r="N9" t="n">
-        <v>36.27537091671674</v>
+        <v>36.22840163624001</v>
       </c>
       <c r="O9" t="n">
-        <v>6.022903860823011</v>
+        <v>6.019003375662786</v>
       </c>
       <c r="P9" t="n">
-        <v>333.3375283557821</v>
+        <v>333.3477245433671</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30657,28 +30706,28 @@
         <v>0.08550000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3450947798722035</v>
+        <v>-0.3472679704790506</v>
       </c>
       <c r="J10" t="n">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="K10" t="n">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01428119986862053</v>
+        <v>0.01451470051075565</v>
       </c>
       <c r="M10" t="n">
-        <v>17.3373568960232</v>
+        <v>17.3207896450932</v>
       </c>
       <c r="N10" t="n">
-        <v>452.337483007109</v>
+        <v>451.6453849909298</v>
       </c>
       <c r="O10" t="n">
-        <v>21.26822707719449</v>
+        <v>21.25195014559675</v>
       </c>
       <c r="P10" t="n">
-        <v>327.9878731690533</v>
+        <v>328.0099723716488</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -30720,7 +30769,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K598"/>
+  <dimension ref="A1:K599"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64809,6 +64858,63 @@
         </is>
       </c>
     </row>
+    <row r="599">
+      <c r="A599" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:19:37+00:00</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>-42.1230476386624,171.32829259931248</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>-42.122373797627915,171.3284038503355</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>-42.12169581818834,171.3284824303573</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>-42.12103166645168,171.32860893535366</t>
+        </is>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>-42.120367057947135,171.32870917978417</t>
+        </is>
+      </c>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>-42.119706547695834,171.3288477426302</t>
+        </is>
+      </c>
+      <c r="H599" t="inlineStr">
+        <is>
+          <t>-42.119040153396774,171.3289633800246</t>
+        </is>
+      </c>
+      <c r="I599" t="inlineStr">
+        <is>
+          <t>-42.11836426801789,171.32910887565464</t>
+        </is>
+      </c>
+      <c r="J599" t="inlineStr">
+        <is>
+          <t>-42.11768228781051,171.3291689193051</t>
+        </is>
+      </c>
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0383/nzd0383.xlsx
+++ b/data/nzd0383/nzd0383.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K599"/>
+  <dimension ref="A1:K600"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23805,6 +23805,45 @@
         <v>312.63</v>
       </c>
       <c r="K599" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:13:26+00:00</t>
+        </is>
+      </c>
+      <c r="B600" t="n">
+        <v>313.26</v>
+      </c>
+      <c r="C600" t="n">
+        <v>326.96</v>
+      </c>
+      <c r="D600" t="n">
+        <v>338.13</v>
+      </c>
+      <c r="E600" t="n">
+        <v>342.81</v>
+      </c>
+      <c r="F600" t="n">
+        <v>346.53</v>
+      </c>
+      <c r="G600" t="n">
+        <v>346.3</v>
+      </c>
+      <c r="H600" t="n">
+        <v>337.96</v>
+      </c>
+      <c r="I600" t="n">
+        <v>326.68</v>
+      </c>
+      <c r="J600" t="n">
+        <v>318.41</v>
+      </c>
+      <c r="K600" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -23821,7 +23860,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B609"/>
+  <dimension ref="A1:B610"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29914,6 +29953,16 @@
       </c>
       <c r="B609" t="n">
         <v>-0.75</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B610" t="n">
+        <v>1.11</v>
       </c>
     </row>
   </sheetData>
@@ -30082,28 +30131,28 @@
         <v>0.055</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3655997572431984</v>
+        <v>-0.373330087901776</v>
       </c>
       <c r="J2" t="n">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="K2" t="n">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03627144705031426</v>
+        <v>0.03775768775241362</v>
       </c>
       <c r="M2" t="n">
-        <v>11.44131453536513</v>
+        <v>11.45947406348005</v>
       </c>
       <c r="N2" t="n">
-        <v>195.896956843973</v>
+        <v>196.3882277049688</v>
       </c>
       <c r="O2" t="n">
-        <v>13.99631940347079</v>
+        <v>14.01385841604548</v>
       </c>
       <c r="P2" t="n">
-        <v>345.1546338093961</v>
+        <v>345.2333225655146</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -30160,28 +30209,28 @@
         <v>0.0579</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4051798232118687</v>
+        <v>-0.4051572457698751</v>
       </c>
       <c r="J3" t="n">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="K3" t="n">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2089864180355184</v>
+        <v>0.2096348231048908</v>
       </c>
       <c r="M3" t="n">
-        <v>4.878957861225541</v>
+        <v>4.870925273687791</v>
       </c>
       <c r="N3" t="n">
-        <v>34.27579584300464</v>
+        <v>34.21858112736714</v>
       </c>
       <c r="O3" t="n">
-        <v>5.854553428145023</v>
+        <v>5.849665044031765</v>
       </c>
       <c r="P3" t="n">
-        <v>337.6317714449857</v>
+        <v>337.6315416241792</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30238,28 +30287,28 @@
         <v>0.0607</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1621308757710853</v>
+        <v>-0.1620807447487918</v>
       </c>
       <c r="J4" t="n">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="K4" t="n">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0516744698317021</v>
+        <v>0.05184181632602691</v>
       </c>
       <c r="M4" t="n">
-        <v>4.008784506424503</v>
+        <v>4.002353107972342</v>
       </c>
       <c r="N4" t="n">
-        <v>26.60963504119652</v>
+        <v>26.56524602442083</v>
       </c>
       <c r="O4" t="n">
-        <v>5.158452775900591</v>
+        <v>5.154148428636959</v>
       </c>
       <c r="P4" t="n">
-        <v>342.2814967815649</v>
+        <v>342.2809864867326</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30316,28 +30365,28 @@
         <v>0.0618</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2233787288323817</v>
+        <v>-0.2236227508363517</v>
       </c>
       <c r="J5" t="n">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="K5" t="n">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08801505917451302</v>
+        <v>0.08851274663807251</v>
       </c>
       <c r="M5" t="n">
-        <v>4.376693594935007</v>
+        <v>4.370597562189875</v>
       </c>
       <c r="N5" t="n">
-        <v>28.51939840443152</v>
+        <v>28.47260213868006</v>
       </c>
       <c r="O5" t="n">
-        <v>5.340355644002702</v>
+        <v>5.335972464198074</v>
       </c>
       <c r="P5" t="n">
-        <v>349.4342864800424</v>
+        <v>349.4367704343267</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30394,28 +30443,28 @@
         <v>0.053</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3257005843022029</v>
+        <v>-0.324988544078825</v>
       </c>
       <c r="J6" t="n">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="K6" t="n">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1757843966420661</v>
+        <v>0.1756973277039164</v>
       </c>
       <c r="M6" t="n">
-        <v>4.153973574925915</v>
+        <v>4.150096816188618</v>
       </c>
       <c r="N6" t="n">
-        <v>27.43617931683756</v>
+        <v>27.39731875765963</v>
       </c>
       <c r="O6" t="n">
-        <v>5.237955642885644</v>
+        <v>5.234244812545515</v>
       </c>
       <c r="P6" t="n">
-        <v>353.1139902957864</v>
+        <v>353.1067422798918</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30472,28 +30521,28 @@
         <v>0.0557</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.254099222154365</v>
+        <v>-0.2544368843862843</v>
       </c>
       <c r="J7" t="n">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="K7" t="n">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1414031696202405</v>
+        <v>0.1422079673201544</v>
       </c>
       <c r="M7" t="n">
-        <v>3.832832070923424</v>
+        <v>3.827945138752897</v>
       </c>
       <c r="N7" t="n">
-        <v>21.62533558161371</v>
+        <v>21.59079448780409</v>
       </c>
       <c r="O7" t="n">
-        <v>4.65030489125323</v>
+        <v>4.646589554480156</v>
       </c>
       <c r="P7" t="n">
-        <v>354.0020347092721</v>
+        <v>354.0054718482758</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30550,28 +30599,28 @@
         <v>0.0546</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1415014979326486</v>
+        <v>-0.142369659665523</v>
       </c>
       <c r="J8" t="n">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="K8" t="n">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03980159249513193</v>
+        <v>0.04041273849130478</v>
       </c>
       <c r="M8" t="n">
-        <v>4.207265922752671</v>
+        <v>4.204205091092899</v>
       </c>
       <c r="N8" t="n">
-        <v>26.64456627155733</v>
+        <v>26.61040556456208</v>
       </c>
       <c r="O8" t="n">
-        <v>5.161837489843838</v>
+        <v>5.158527460871182</v>
       </c>
       <c r="P8" t="n">
-        <v>344.2085821013783</v>
+        <v>344.2174193128621</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30628,28 +30677,28 @@
         <v>0.0518</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.216176772177166</v>
+        <v>-0.2165042781781454</v>
       </c>
       <c r="J9" t="n">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="K9" t="n">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06642679635489035</v>
+        <v>0.06686325156495632</v>
       </c>
       <c r="M9" t="n">
-        <v>4.954376652175919</v>
+        <v>4.947404053862065</v>
       </c>
       <c r="N9" t="n">
-        <v>36.22840163624001</v>
+        <v>36.16938895773426</v>
       </c>
       <c r="O9" t="n">
-        <v>6.019003375662786</v>
+        <v>6.014099180902678</v>
       </c>
       <c r="P9" t="n">
-        <v>333.3477245433671</v>
+        <v>333.3510582998359</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30706,28 +30755,28 @@
         <v>0.08550000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3472679704790506</v>
+        <v>-0.3474070940216218</v>
       </c>
       <c r="J10" t="n">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="K10" t="n">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01451470051075565</v>
+        <v>0.01458395140294177</v>
       </c>
       <c r="M10" t="n">
-        <v>17.3207896450932</v>
+        <v>17.29267003202635</v>
       </c>
       <c r="N10" t="n">
-        <v>451.6453849909298</v>
+        <v>450.8916510649817</v>
       </c>
       <c r="O10" t="n">
-        <v>21.25195014559675</v>
+        <v>21.23420945231966</v>
       </c>
       <c r="P10" t="n">
-        <v>328.0099723716488</v>
+        <v>328.0113885411499</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -30769,7 +30818,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K599"/>
+  <dimension ref="A1:K600"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64915,6 +64964,63 @@
         </is>
       </c>
     </row>
+    <row r="600">
+      <c r="A600" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:13:26+00:00</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>-42.1230511438045,171.3283084867734</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>-42.12237197524039,171.3283948645836</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>-42.121693834914424,171.32847112893316</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>-42.121030418947655,171.32860026659284</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>-42.120364737500715,171.3286902034624</t>
+        </is>
+      </c>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>-42.11970500095809,171.32882692240003</t>
+        </is>
+      </c>
+      <c r="H600" t="inlineStr">
+        <is>
+          <t>-42.11903986036088,171.3289480251079</t>
+        </is>
+      </c>
+      <c r="I600" t="inlineStr">
+        <is>
+          <t>-42.11836484011104,171.3290857882701</t>
+        </is>
+      </c>
+      <c r="J600" t="inlineStr">
+        <is>
+          <t>-42.117686537984234,171.3290992483115</t>
+        </is>
+      </c>
+      <c r="K600" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0383/nzd0383.xlsx
+++ b/data/nzd0383/nzd0383.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K600"/>
+  <dimension ref="A1:K602"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23846,6 +23846,84 @@
       <c r="K600" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:13:10+00:00</t>
+        </is>
+      </c>
+      <c r="B601" t="n">
+        <v>316.22</v>
+      </c>
+      <c r="C601" t="n">
+        <v>330.63</v>
+      </c>
+      <c r="D601" t="n">
+        <v>342.27</v>
+      </c>
+      <c r="E601" t="n">
+        <v>348.14</v>
+      </c>
+      <c r="F601" t="n">
+        <v>351.75</v>
+      </c>
+      <c r="G601" t="n">
+        <v>349.53</v>
+      </c>
+      <c r="H601" t="n">
+        <v>344.19</v>
+      </c>
+      <c r="I601" t="n">
+        <v>331.76</v>
+      </c>
+      <c r="J601" t="n">
+        <v>331.68</v>
+      </c>
+      <c r="K601" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:13:11+00:00</t>
+        </is>
+      </c>
+      <c r="B602" t="n">
+        <v>308.95</v>
+      </c>
+      <c r="C602" t="n">
+        <v>329.16</v>
+      </c>
+      <c r="D602" t="n">
+        <v>340.28</v>
+      </c>
+      <c r="E602" t="n">
+        <v>345.97</v>
+      </c>
+      <c r="F602" t="n">
+        <v>350.82</v>
+      </c>
+      <c r="G602" t="n">
+        <v>348.52</v>
+      </c>
+      <c r="H602" t="n">
+        <v>343.72</v>
+      </c>
+      <c r="I602" t="n">
+        <v>331.6</v>
+      </c>
+      <c r="J602" t="n">
+        <v>323.78</v>
+      </c>
+      <c r="K602" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -23860,7 +23938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B610"/>
+  <dimension ref="A1:B612"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29963,6 +30041,26 @@
       </c>
       <c r="B610" t="n">
         <v>1.11</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B611" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B612" t="n">
+        <v>0.99</v>
       </c>
     </row>
   </sheetData>
@@ -30131,28 +30229,28 @@
         <v>0.055</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.373330087901776</v>
+        <v>-0.3891319673492852</v>
       </c>
       <c r="J2" t="n">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="K2" t="n">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03775768775241362</v>
+        <v>0.04086027581700735</v>
       </c>
       <c r="M2" t="n">
-        <v>11.45947406348005</v>
+        <v>11.49864000860595</v>
       </c>
       <c r="N2" t="n">
-        <v>196.3882277049688</v>
+        <v>197.4746185789088</v>
       </c>
       <c r="O2" t="n">
-        <v>14.01385841604548</v>
+        <v>14.05256626310329</v>
       </c>
       <c r="P2" t="n">
-        <v>345.2333225655146</v>
+        <v>345.3949908966849</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -30209,28 +30307,28 @@
         <v>0.0579</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4051572457698751</v>
+        <v>-0.4030357016766887</v>
       </c>
       <c r="J3" t="n">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="K3" t="n">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2096348231048908</v>
+        <v>0.2090867237593248</v>
       </c>
       <c r="M3" t="n">
-        <v>4.870925273687791</v>
+        <v>4.865245823713647</v>
       </c>
       <c r="N3" t="n">
-        <v>34.21858112736714</v>
+        <v>34.13707645555696</v>
       </c>
       <c r="O3" t="n">
-        <v>5.849665044031765</v>
+        <v>5.842694280514509</v>
       </c>
       <c r="P3" t="n">
-        <v>337.6315416241792</v>
+        <v>337.6098475512521</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30287,28 +30385,28 @@
         <v>0.0607</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1620807447487918</v>
+        <v>-0.1597806962452108</v>
       </c>
       <c r="J4" t="n">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="K4" t="n">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05184181632602691</v>
+        <v>0.05077440692938473</v>
       </c>
       <c r="M4" t="n">
-        <v>4.002353107972342</v>
+        <v>4.000859481072062</v>
       </c>
       <c r="N4" t="n">
-        <v>26.56524602442083</v>
+        <v>26.51612625138085</v>
       </c>
       <c r="O4" t="n">
-        <v>5.154148428636959</v>
+        <v>5.149381152272654</v>
       </c>
       <c r="P4" t="n">
-        <v>342.2809864867326</v>
+        <v>342.2574690617723</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30365,28 +30463,28 @@
         <v>0.0618</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2236227508363517</v>
+        <v>-0.2211397743206258</v>
       </c>
       <c r="J5" t="n">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="K5" t="n">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08851274663807251</v>
+        <v>0.08724573244045108</v>
       </c>
       <c r="M5" t="n">
-        <v>4.370597562189875</v>
+        <v>4.367398966489094</v>
       </c>
       <c r="N5" t="n">
-        <v>28.47260213868006</v>
+        <v>28.4236785564928</v>
       </c>
       <c r="O5" t="n">
-        <v>5.335972464198074</v>
+        <v>5.331386175892045</v>
       </c>
       <c r="P5" t="n">
-        <v>349.4367704343267</v>
+        <v>349.4113826765262</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30443,28 +30541,28 @@
         <v>0.053</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.324988544078825</v>
+        <v>-0.3202389697772244</v>
       </c>
       <c r="J6" t="n">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="K6" t="n">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1756973277039164</v>
+        <v>0.1718302840585778</v>
       </c>
       <c r="M6" t="n">
-        <v>4.150096816188618</v>
+        <v>4.156864035737678</v>
       </c>
       <c r="N6" t="n">
-        <v>27.39731875765963</v>
+        <v>27.46027467812625</v>
       </c>
       <c r="O6" t="n">
-        <v>5.234244812545515</v>
+        <v>5.240255211163503</v>
       </c>
       <c r="P6" t="n">
-        <v>353.1067422798918</v>
+        <v>353.058164114635</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30521,28 +30619,28 @@
         <v>0.0557</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2544368843862843</v>
+        <v>-0.2531902362940903</v>
       </c>
       <c r="J7" t="n">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="K7" t="n">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1422079673201544</v>
+        <v>0.1419378583789288</v>
       </c>
       <c r="M7" t="n">
-        <v>3.827945138752897</v>
+        <v>3.821498866948289</v>
       </c>
       <c r="N7" t="n">
-        <v>21.59079448780409</v>
+        <v>21.5303594686941</v>
       </c>
       <c r="O7" t="n">
-        <v>4.646589554480156</v>
+        <v>4.640081838577214</v>
       </c>
       <c r="P7" t="n">
-        <v>354.0054718482758</v>
+        <v>353.9927248400446</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30599,28 +30697,28 @@
         <v>0.0546</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.142369659665523</v>
+        <v>-0.1399138838281915</v>
       </c>
       <c r="J8" t="n">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="K8" t="n">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04041273849130478</v>
+        <v>0.03933268459255979</v>
       </c>
       <c r="M8" t="n">
-        <v>4.204205091092899</v>
+        <v>4.202390956766637</v>
       </c>
       <c r="N8" t="n">
-        <v>26.61040556456208</v>
+        <v>26.56304938565581</v>
       </c>
       <c r="O8" t="n">
-        <v>5.158527460871182</v>
+        <v>5.153935329983857</v>
       </c>
       <c r="P8" t="n">
-        <v>344.2174193128621</v>
+        <v>344.1923018424272</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30677,28 +30775,28 @@
         <v>0.0518</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2165042781781454</v>
+        <v>-0.2136586006642859</v>
       </c>
       <c r="J9" t="n">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="K9" t="n">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06686325156495632</v>
+        <v>0.06563529076813435</v>
       </c>
       <c r="M9" t="n">
-        <v>4.947404053862065</v>
+        <v>4.946794097720183</v>
       </c>
       <c r="N9" t="n">
-        <v>36.16938895773426</v>
+        <v>36.10411073221618</v>
       </c>
       <c r="O9" t="n">
-        <v>6.014099180902678</v>
+        <v>6.008669630809817</v>
       </c>
       <c r="P9" t="n">
-        <v>333.3510582998359</v>
+        <v>333.3219511465157</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30755,28 +30853,28 @@
         <v>0.08550000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3474070940216218</v>
+        <v>-0.3411793742442484</v>
       </c>
       <c r="J10" t="n">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="K10" t="n">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01458395140294177</v>
+        <v>0.01417658889975926</v>
       </c>
       <c r="M10" t="n">
-        <v>17.29267003202635</v>
+        <v>17.25910225910872</v>
       </c>
       <c r="N10" t="n">
-        <v>450.8916510649817</v>
+        <v>449.7071558820669</v>
       </c>
       <c r="O10" t="n">
-        <v>21.23420945231966</v>
+        <v>21.20629991021694</v>
       </c>
       <c r="P10" t="n">
-        <v>328.0113885411499</v>
+        <v>327.9477235270874</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -30818,7 +30916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K600"/>
+  <dimension ref="A1:K602"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65021,6 +65119,120 @@
         </is>
       </c>
     </row>
+    <row r="601">
+      <c r="A601" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:13:10+00:00</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>-42.123043570648015,171.3282741605827</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>-42.122363289305916,171.32835203639686</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>-42.12168528203303,171.32842239155008</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>-42.12102131043975,171.32853697277466</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>-42.120357119409434,171.32862790385042</t>
+        </is>
+      </c>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>-42.119702113108204,171.32878804995025</t>
+        </is>
+      </c>
+      <c r="H601" t="inlineStr">
+        <is>
+          <t>-42.11903842284006,171.3288727013858</t>
+        </is>
+      </c>
+      <c r="I601" t="inlineStr">
+        <is>
+          <t>-42.11836636167645,171.3290243830785</t>
+        </is>
+      </c>
+      <c r="J601" t="inlineStr">
+        <is>
+          <t>-42.117696295575264,171.32893929428752</t>
+        </is>
+      </c>
+      <c r="K601" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:13:11+00:00</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>-42.12306217091628,171.32835846850543</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>-42.12236676841508,171.3283691910097</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>-42.12168939320321,171.32844581845472</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>-42.121025018785794,171.3285627415501</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>-42.12035847665803,171.3286390032054</t>
+        </is>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>-42.11970301612149,171.32880020511215</t>
+        </is>
+      </c>
+      <c r="H602" t="inlineStr">
+        <is>
+          <t>-42.119038531290386,171.3288783839136</t>
+        </is>
+      </c>
+      <c r="I602" t="inlineStr">
+        <is>
+          <t>-42.11836631375364,171.3290263171003</t>
+        </is>
+      </c>
+      <c r="J602" t="inlineStr">
+        <is>
+          <t>-42.117690486636974,171.3290345193709</t>
+        </is>
+      </c>
+      <c r="K602" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0383/nzd0383.xlsx
+++ b/data/nzd0383/nzd0383.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K602"/>
+  <dimension ref="A1:K605"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23922,6 +23922,123 @@
         <v>323.78</v>
       </c>
       <c r="K602" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:19:05+00:00</t>
+        </is>
+      </c>
+      <c r="B603" t="n">
+        <v>320.58</v>
+      </c>
+      <c r="C603" t="n">
+        <v>328.37</v>
+      </c>
+      <c r="D603" t="n">
+        <v>338.6</v>
+      </c>
+      <c r="E603" t="n">
+        <v>344.92</v>
+      </c>
+      <c r="F603" t="n">
+        <v>349.81</v>
+      </c>
+      <c r="G603" t="n">
+        <v>348.03</v>
+      </c>
+      <c r="H603" t="n">
+        <v>342.6</v>
+      </c>
+      <c r="I603" t="n">
+        <v>330.85</v>
+      </c>
+      <c r="J603" t="n">
+        <v>315.84</v>
+      </c>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:13:06+00:00</t>
+        </is>
+      </c>
+      <c r="B604" t="n">
+        <v>325.07</v>
+      </c>
+      <c r="C604" t="n">
+        <v>327.81</v>
+      </c>
+      <c r="D604" t="n">
+        <v>338.5</v>
+      </c>
+      <c r="E604" t="n">
+        <v>345.29</v>
+      </c>
+      <c r="F604" t="n">
+        <v>348.3</v>
+      </c>
+      <c r="G604" t="n">
+        <v>347.2</v>
+      </c>
+      <c r="H604" t="n">
+        <v>342.81</v>
+      </c>
+      <c r="I604" t="n">
+        <v>330.83</v>
+      </c>
+      <c r="J604" t="n">
+        <v>312.92</v>
+      </c>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:12:49+00:00</t>
+        </is>
+      </c>
+      <c r="B605" t="n">
+        <v>338.42</v>
+      </c>
+      <c r="C605" t="n">
+        <v>324.47</v>
+      </c>
+      <c r="D605" t="n">
+        <v>335.56</v>
+      </c>
+      <c r="E605" t="n">
+        <v>343.52</v>
+      </c>
+      <c r="F605" t="n">
+        <v>346.52</v>
+      </c>
+      <c r="G605" t="n">
+        <v>345.34</v>
+      </c>
+      <c r="H605" t="n">
+        <v>342.66</v>
+      </c>
+      <c r="I605" t="n">
+        <v>331.67</v>
+      </c>
+      <c r="J605" t="n">
+        <v>312.92</v>
+      </c>
+      <c r="K605" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -23938,7 +24055,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B612"/>
+  <dimension ref="A1:B615"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30061,6 +30178,36 @@
       </c>
       <c r="B612" t="n">
         <v>0.99</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B613" t="n">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B614" t="n">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B615" t="n">
+        <v>1.52</v>
       </c>
     </row>
   </sheetData>
@@ -30229,28 +30376,28 @@
         <v>0.055</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3891319673492852</v>
+        <v>-0.396329216406831</v>
       </c>
       <c r="J2" t="n">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="K2" t="n">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04086027581700735</v>
+        <v>0.0427082823038849</v>
       </c>
       <c r="M2" t="n">
-        <v>11.49864000860595</v>
+        <v>11.48859045002656</v>
       </c>
       <c r="N2" t="n">
-        <v>197.4746185789088</v>
+        <v>197.0172386532067</v>
       </c>
       <c r="O2" t="n">
-        <v>14.05256626310329</v>
+        <v>14.03628293577779</v>
       </c>
       <c r="P2" t="n">
-        <v>345.3949908966849</v>
+        <v>345.4688082045587</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -30307,28 +30454,28 @@
         <v>0.0579</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4030357016766887</v>
+        <v>-0.4029990782992186</v>
       </c>
       <c r="J3" t="n">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="K3" t="n">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2090867237593248</v>
+        <v>0.2110046704513944</v>
       </c>
       <c r="M3" t="n">
-        <v>4.865245823713647</v>
+        <v>4.849101274122002</v>
       </c>
       <c r="N3" t="n">
-        <v>34.13707645555696</v>
+        <v>33.98210862124134</v>
       </c>
       <c r="O3" t="n">
-        <v>5.842694280514509</v>
+        <v>5.829417519893505</v>
       </c>
       <c r="P3" t="n">
-        <v>337.6098475512521</v>
+        <v>337.6094871163536</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30385,28 +30532,28 @@
         <v>0.0607</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1597806962452108</v>
+        <v>-0.1602330210062561</v>
       </c>
       <c r="J4" t="n">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="K4" t="n">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05077440692938473</v>
+        <v>0.05162036976099937</v>
       </c>
       <c r="M4" t="n">
-        <v>4.000859481072062</v>
+        <v>3.986716268110309</v>
       </c>
       <c r="N4" t="n">
-        <v>26.51612625138085</v>
+        <v>26.39520272540377</v>
       </c>
       <c r="O4" t="n">
-        <v>5.149381152272654</v>
+        <v>5.137626176105437</v>
       </c>
       <c r="P4" t="n">
-        <v>342.2574690617723</v>
+        <v>342.2621253158632</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30463,28 +30610,28 @@
         <v>0.0618</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2211397743206258</v>
+        <v>-0.2200314228242431</v>
       </c>
       <c r="J5" t="n">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="K5" t="n">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08724573244045108</v>
+        <v>0.08739086992894463</v>
       </c>
       <c r="M5" t="n">
-        <v>4.367398966489094</v>
+        <v>4.350708750255804</v>
       </c>
       <c r="N5" t="n">
-        <v>28.4236785564928</v>
+        <v>28.29098150713401</v>
       </c>
       <c r="O5" t="n">
-        <v>5.331386175892045</v>
+        <v>5.318926725114195</v>
       </c>
       <c r="P5" t="n">
-        <v>349.4113826765262</v>
+        <v>349.4000113117542</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30541,28 +30688,28 @@
         <v>0.053</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3202389697772244</v>
+        <v>-0.3164079178608302</v>
       </c>
       <c r="J6" t="n">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="K6" t="n">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1718302840585778</v>
+        <v>0.1697512927832445</v>
       </c>
       <c r="M6" t="n">
-        <v>4.156864035737678</v>
+        <v>4.152937922524015</v>
       </c>
       <c r="N6" t="n">
-        <v>27.46027467812625</v>
+        <v>27.399942857255</v>
       </c>
       <c r="O6" t="n">
-        <v>5.240255211163503</v>
+        <v>5.23449547303797</v>
       </c>
       <c r="P6" t="n">
-        <v>353.058164114635</v>
+        <v>353.0188466556409</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30619,28 +30766,28 @@
         <v>0.0557</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2531902362940903</v>
+        <v>-0.2535746333648412</v>
       </c>
       <c r="J7" t="n">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="K7" t="n">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1419378583789288</v>
+        <v>0.1437601781952322</v>
       </c>
       <c r="M7" t="n">
-        <v>3.821498866948289</v>
+        <v>3.806898134522084</v>
       </c>
       <c r="N7" t="n">
-        <v>21.5303594686941</v>
+        <v>21.43030173576886</v>
       </c>
       <c r="O7" t="n">
-        <v>4.640081838577214</v>
+        <v>4.629287389628004</v>
       </c>
       <c r="P7" t="n">
-        <v>353.9927248400446</v>
+        <v>353.9966807959988</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30697,28 +30844,28 @@
         <v>0.0546</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1399138838281915</v>
+        <v>-0.1376001047361632</v>
       </c>
       <c r="J8" t="n">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="K8" t="n">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03933268459255979</v>
+        <v>0.03850580010935534</v>
       </c>
       <c r="M8" t="n">
-        <v>4.202390956766637</v>
+        <v>4.192872401653936</v>
       </c>
       <c r="N8" t="n">
-        <v>26.56304938565581</v>
+        <v>26.45561729732849</v>
       </c>
       <c r="O8" t="n">
-        <v>5.153935329983857</v>
+        <v>5.143502434852004</v>
       </c>
       <c r="P8" t="n">
-        <v>344.1923018424272</v>
+        <v>344.1685493282195</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30775,28 +30922,28 @@
         <v>0.0518</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2136586006642859</v>
+        <v>-0.2100349998862978</v>
       </c>
       <c r="J9" t="n">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="K9" t="n">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06563529076813435</v>
+        <v>0.06419488728910039</v>
       </c>
       <c r="M9" t="n">
-        <v>4.946794097720183</v>
+        <v>4.942412034779603</v>
       </c>
       <c r="N9" t="n">
-        <v>36.10411073221618</v>
+        <v>35.98555196566222</v>
       </c>
       <c r="O9" t="n">
-        <v>6.008669630809817</v>
+        <v>5.998795876312364</v>
       </c>
       <c r="P9" t="n">
-        <v>333.3219511465157</v>
+        <v>333.2847486253702</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30853,28 +31000,28 @@
         <v>0.08550000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3411793742442484</v>
+        <v>-0.3462876572972992</v>
       </c>
       <c r="J10" t="n">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="K10" t="n">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01417658889975926</v>
+        <v>0.01476996403971909</v>
       </c>
       <c r="M10" t="n">
-        <v>17.25910225910872</v>
+        <v>17.20222173959577</v>
       </c>
       <c r="N10" t="n">
-        <v>449.7071558820669</v>
+        <v>447.6020674740459</v>
       </c>
       <c r="O10" t="n">
-        <v>21.20629991021694</v>
+        <v>21.15660812781779</v>
       </c>
       <c r="P10" t="n">
-        <v>327.9477235270874</v>
+        <v>328.0001705521187</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -30916,7 +31063,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K602"/>
+  <dimension ref="A1:K605"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65233,6 +65380,177 @@
         </is>
       </c>
     </row>
+    <row r="603">
+      <c r="A603" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:19:05+00:00</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>-42.12303241557473,171.328223599047</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>-42.12236863813937,171.3283784101562</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>-42.12169286393616,171.32846559594455</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>-42.12102681314473,171.32857521031355</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>-42.120359950658006,171.3286510573442</t>
+        </is>
+      </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>-42.11970345421658,171.32880610217103</t>
+        </is>
+      </c>
+      <c r="H603" t="inlineStr">
+        <is>
+          <t>-42.119038789724065,171.3288919252566</t>
+        </is>
+      </c>
+      <c r="I603" t="inlineStr">
+        <is>
+          <t>-42.11836608911501,171.32903538282753</t>
+        </is>
+      </c>
+      <c r="J603" t="inlineStr">
+        <is>
+          <t>-42.11768464820636,171.32913022659164</t>
+        </is>
+      </c>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:13:06+00:00</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>-42.12302092787305,171.3281715299618</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>-42.1223699635131,171.32838494524773</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>-42.121693070527314,171.32846677317616</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>-42.121026180846975,171.3285708165587</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>-42.12036215435859,171.32866907887956</t>
+        </is>
+      </c>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>-42.119704196295345,171.3288160910669</t>
+        </is>
+      </c>
+      <c r="H604" t="inlineStr">
+        <is>
+          <t>-42.11903874126787,171.3288893862548</t>
+        </is>
+      </c>
+      <c r="I604" t="inlineStr">
+        <is>
+          <t>-42.11836608312462,171.32903562458023</t>
+        </is>
+      </c>
+      <c r="J604" t="inlineStr">
+        <is>
+          <t>-42.11768250105555,171.3291654237018</t>
+        </is>
+      </c>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:12:49+00:00</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>-42.12298677165122,171.32801671442286</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>-42.1223778684131,171.32842392240659</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>-42.12169914430151,171.328501383789</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>-42.12102920562122,171.32859183533265</t>
+        </is>
+      </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>-42.12036475209474,171.32869032281033</t>
+        </is>
+      </c>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>-42.119705859263895,171.3288384758224</t>
+        </is>
+      </c>
+      <c r="H605" t="inlineStr">
+        <is>
+          <t>-42.119038775879446,171.32889119982752</t>
+        </is>
+      </c>
+      <c r="I605" t="inlineStr">
+        <is>
+          <t>-42.11836633471987,171.32902547096577</t>
+        </is>
+      </c>
+      <c r="J605" t="inlineStr">
+        <is>
+          <t>-42.11768250105555,171.3291654237018</t>
+        </is>
+      </c>
+      <c r="K605" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0383/nzd0383.xlsx
+++ b/data/nzd0383/nzd0383.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K605"/>
+  <dimension ref="A1:K607"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24041,6 +24041,84 @@
       <c r="K605" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:18:51+00:00</t>
+        </is>
+      </c>
+      <c r="B606" t="n">
+        <v>338.31</v>
+      </c>
+      <c r="C606" t="n">
+        <v>324.09</v>
+      </c>
+      <c r="D606" t="n">
+        <v>335.14</v>
+      </c>
+      <c r="E606" t="n">
+        <v>341.93</v>
+      </c>
+      <c r="F606" t="n">
+        <v>344.98</v>
+      </c>
+      <c r="G606" t="n">
+        <v>343.57</v>
+      </c>
+      <c r="H606" t="n">
+        <v>340.55</v>
+      </c>
+      <c r="I606" t="n">
+        <v>330.81</v>
+      </c>
+      <c r="J606" t="n">
+        <v>309.45</v>
+      </c>
+      <c r="K606" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:18:47+00:00</t>
+        </is>
+      </c>
+      <c r="B607" t="n">
+        <v>338.31</v>
+      </c>
+      <c r="C607" t="n">
+        <v>324.09</v>
+      </c>
+      <c r="D607" t="n">
+        <v>335.14</v>
+      </c>
+      <c r="E607" t="n">
+        <v>345.22</v>
+      </c>
+      <c r="F607" t="n">
+        <v>344.98</v>
+      </c>
+      <c r="G607" t="n">
+        <v>343.57</v>
+      </c>
+      <c r="H607" t="n">
+        <v>340.55</v>
+      </c>
+      <c r="I607" t="n">
+        <v>330.81</v>
+      </c>
+      <c r="J607" t="n">
+        <v>359.16</v>
+      </c>
+      <c r="K607" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -24055,7 +24133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B615"/>
+  <dimension ref="A1:B617"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30208,6 +30286,26 @@
       </c>
       <c r="B615" t="n">
         <v>1.52</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B616" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B617" t="n">
+        <v>0.85</v>
       </c>
     </row>
   </sheetData>
@@ -30376,28 +30474,28 @@
         <v>0.055</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.396329216406831</v>
+        <v>-0.3939427699099187</v>
       </c>
       <c r="J2" t="n">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="K2" t="n">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0427082823038849</v>
+        <v>0.04253807366892626</v>
       </c>
       <c r="M2" t="n">
-        <v>11.48859045002656</v>
+        <v>11.46164767669968</v>
       </c>
       <c r="N2" t="n">
-        <v>197.0172386532067</v>
+        <v>196.4063497272401</v>
       </c>
       <c r="O2" t="n">
-        <v>14.03628293577779</v>
+        <v>14.01450497617522</v>
       </c>
       <c r="P2" t="n">
-        <v>345.4688082045587</v>
+        <v>345.4442080216616</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -30454,28 +30552,28 @@
         <v>0.0579</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4029990782992186</v>
+        <v>-0.4048609731302531</v>
       </c>
       <c r="J3" t="n">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="K3" t="n">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2110046704513944</v>
+        <v>0.2137849837144929</v>
       </c>
       <c r="M3" t="n">
-        <v>4.849101274122002</v>
+        <v>4.841648069048158</v>
       </c>
       <c r="N3" t="n">
-        <v>33.98210862124134</v>
+        <v>33.89389878895279</v>
       </c>
       <c r="O3" t="n">
-        <v>5.829417519893505</v>
+        <v>5.821846682020473</v>
       </c>
       <c r="P3" t="n">
-        <v>337.6094871163536</v>
+        <v>337.6286800444108</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30532,28 +30630,28 @@
         <v>0.0607</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1602330210062561</v>
+        <v>-0.1621745412018537</v>
       </c>
       <c r="J4" t="n">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="K4" t="n">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05162036976099937</v>
+        <v>0.05316969816188366</v>
       </c>
       <c r="M4" t="n">
-        <v>3.986716268110309</v>
+        <v>3.982159803915389</v>
       </c>
       <c r="N4" t="n">
-        <v>26.39520272540377</v>
+        <v>26.3341236909796</v>
       </c>
       <c r="O4" t="n">
-        <v>5.137626176105437</v>
+        <v>5.131678447738088</v>
       </c>
       <c r="P4" t="n">
-        <v>342.2621253158632</v>
+        <v>342.2821390530398</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30610,28 +30708,28 @@
         <v>0.0618</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2200314228242431</v>
+        <v>-0.2199761738292129</v>
       </c>
       <c r="J5" t="n">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="K5" t="n">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08739086992894463</v>
+        <v>0.08797383219148946</v>
       </c>
       <c r="M5" t="n">
-        <v>4.350708750255804</v>
+        <v>4.341772138058738</v>
       </c>
       <c r="N5" t="n">
-        <v>28.29098150713401</v>
+        <v>28.20659339387771</v>
       </c>
       <c r="O5" t="n">
-        <v>5.318926725114195</v>
+        <v>5.31098798660642</v>
       </c>
       <c r="P5" t="n">
-        <v>349.4000113117542</v>
+        <v>349.39943670347</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30688,28 +30786,28 @@
         <v>0.053</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3164079178608302</v>
+        <v>-0.3161012933150559</v>
       </c>
       <c r="J6" t="n">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="K6" t="n">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1697512927832445</v>
+        <v>0.1706191625603873</v>
       </c>
       <c r="M6" t="n">
-        <v>4.152937922524015</v>
+        <v>4.140560210555773</v>
       </c>
       <c r="N6" t="n">
-        <v>27.399942857255</v>
+        <v>27.31016336633643</v>
       </c>
       <c r="O6" t="n">
-        <v>5.23449547303797</v>
+        <v>5.225912682616926</v>
       </c>
       <c r="P6" t="n">
-        <v>353.0188466556409</v>
+        <v>353.0156858718848</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30766,28 +30864,28 @@
         <v>0.0557</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2535746333648412</v>
+        <v>-0.2560698617430761</v>
       </c>
       <c r="J7" t="n">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="K7" t="n">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1437601781952322</v>
+        <v>0.1469503919509013</v>
       </c>
       <c r="M7" t="n">
-        <v>3.806898134522084</v>
+        <v>3.805533330740982</v>
       </c>
       <c r="N7" t="n">
-        <v>21.43030173576886</v>
+        <v>21.40257534615597</v>
       </c>
       <c r="O7" t="n">
-        <v>4.629287389628004</v>
+        <v>4.626291748923318</v>
       </c>
       <c r="P7" t="n">
-        <v>353.9966807959988</v>
+        <v>354.0224023115123</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30844,28 +30942,28 @@
         <v>0.0546</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1376001047361632</v>
+        <v>-0.1375491676840498</v>
       </c>
       <c r="J8" t="n">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="K8" t="n">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03850580010935534</v>
+        <v>0.03877948328363101</v>
       </c>
       <c r="M8" t="n">
-        <v>4.192872401653936</v>
+        <v>4.179283990502877</v>
       </c>
       <c r="N8" t="n">
-        <v>26.45561729732849</v>
+        <v>26.3683229551443</v>
       </c>
       <c r="O8" t="n">
-        <v>5.143502434852004</v>
+        <v>5.135009537979876</v>
       </c>
       <c r="P8" t="n">
-        <v>344.1685493282195</v>
+        <v>344.1680242499421</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30922,28 +31020,28 @@
         <v>0.0518</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2100349998862978</v>
+        <v>-0.2078610496172893</v>
       </c>
       <c r="J9" t="n">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="K9" t="n">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06419488728910039</v>
+        <v>0.06338211290805884</v>
       </c>
       <c r="M9" t="n">
-        <v>4.942412034779603</v>
+        <v>4.938111260703</v>
       </c>
       <c r="N9" t="n">
-        <v>35.98555196566222</v>
+        <v>35.89942795735479</v>
       </c>
       <c r="O9" t="n">
-        <v>5.998795876312364</v>
+        <v>5.991613134820605</v>
       </c>
       <c r="P9" t="n">
-        <v>333.2847486253702</v>
+        <v>333.2623389203484</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31000,28 +31098,28 @@
         <v>0.08550000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3462876572972992</v>
+        <v>-0.335555482969118</v>
       </c>
       <c r="J10" t="n">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="K10" t="n">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01476996403971909</v>
+        <v>0.01390551519320282</v>
       </c>
       <c r="M10" t="n">
-        <v>17.20222173959577</v>
+        <v>17.2185496011504</v>
       </c>
       <c r="N10" t="n">
-        <v>447.6020674740459</v>
+        <v>448.9579710743819</v>
       </c>
       <c r="O10" t="n">
-        <v>21.15660812781779</v>
+        <v>21.1886283433917</v>
       </c>
       <c r="P10" t="n">
-        <v>328.0001705521187</v>
+        <v>327.8894635081767</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -31063,7 +31161,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K605"/>
+  <dimension ref="A1:K607"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65551,6 +65649,120 @@
         </is>
       </c>
     </row>
+    <row r="606">
+      <c r="A606" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:18:51+00:00</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>-42.12298705308908,171.32801799005577</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>-42.122378767772155,171.3284283569343</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>-42.121700011982696,171.32850632816283</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>-42.121031922788035,171.3286107166059</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>-42.120366999571154,171.32870870239242</t>
+        </is>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>-42.11970744176217,171.3288597774458</t>
+        </is>
+      </c>
+      <c r="H606" t="inlineStr">
+        <is>
+          <t>-42.119039262745865,171.32891671075092</t>
+        </is>
+      </c>
+      <c r="I606" t="inlineStr">
+        <is>
+          <t>-42.11836607713424,171.329035866333</t>
+        </is>
+      </c>
+      <c r="J606" t="inlineStr">
+        <is>
+          <t>-42.11767994946152,171.32920725040196</t>
+        </is>
+      </c>
+      <c r="K606" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:18:47+00:00</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>-42.12298705308908,171.32801799005577</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>-42.122378767772155,171.3284283569343</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>-42.121700011982696,171.32850632816283</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>-42.12102630047089,171.32857164780964</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>-42.120366999571154,171.32870870239242</t>
+        </is>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>-42.11970744176217,171.3288597774458</t>
+        </is>
+      </c>
+      <c r="H607" t="inlineStr">
+        <is>
+          <t>-42.119039262745865,171.32891671075092</t>
+        </is>
+      </c>
+      <c r="I607" t="inlineStr">
+        <is>
+          <t>-42.11836607713424,171.329035866333</t>
+        </is>
+      </c>
+      <c r="J607" t="inlineStr">
+        <is>
+          <t>-42.11771650123852,171.32860805552718</t>
+        </is>
+      </c>
+      <c r="K607" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
